--- a/pinout.xlsx
+++ b/pinout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/821494d98a70297a/Documents/STM32CubeIDE/HID_Devices/Throttle_Extender_with_STM32/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_AD4D066CA252ABDACC10487B9997F50673EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7BE14C9-FF46-45E3-B258-DF321635280D}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_AD4D066CA252ABDACC10487B9997F50673EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDE9FEA-B2E7-41EB-8AFC-78B5930DD945}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>TDC_PUSH</t>
     <phoneticPr fontId="5"/>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>PADDING</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>TDC2_PUSH</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -140,6 +136,18 @@
   </si>
   <si>
     <t>11byte</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>BRK_MIDDLE</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>MSL_MIDDLE</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>PINKY_MIDDLE</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -453,7 +461,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1"/>
@@ -489,8 +497,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="5" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="20% - アクセント 2" xfId="3" builtinId="34"/>
@@ -815,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>1</v>
@@ -853,40 +860,44 @@
         <v>11</v>
       </c>
       <c r="H5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="19" t="s">
         <v>21</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="3:10" ht="19.5" thickBot="1">
       <c r="C6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="G6" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36"/>
+      <c r="H6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="3:10">
       <c r="C7" s="23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="13">
         <v>1</v>
@@ -938,7 +949,7 @@
     </row>
     <row r="9" spans="3:10">
       <c r="C9" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -990,7 +1001,7 @@
     </row>
     <row r="11" spans="3:10">
       <c r="C11" s="25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="26">
         <v>1</v>
@@ -1042,7 +1053,7 @@
     </row>
     <row r="13" spans="3:10">
       <c r="C13" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="31">
         <v>1</v>
@@ -1094,18 +1105,18 @@
     </row>
     <row r="16" spans="3:10">
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="3:4">
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
